--- a/grupos/1AM - Estadisticos 20231.xlsx
+++ b/grupos/1AM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
+    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -212,13 +212,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>TELLO</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
   </si>
   <si>
     <t>CASTRO</t>
@@ -230,46 +230,40 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
     <t>SANTOS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>UTRERA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>JUAN YAHEL</t>
-  </si>
-  <si>
-    <t>ANGEL YAMIL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>JOEL MIGUEL</t>
+  </si>
+  <si>
+    <t>ERICK ANGEL</t>
   </si>
   <si>
     <t>OMAR DAVID</t>
@@ -281,16 +275,10 @@
     <t>JAIME</t>
   </si>
   <si>
-    <t>HERSON</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSUE YAHIR</t>
   </si>
 </sst>
 </file>
@@ -817,19 +805,19 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -865,13 +853,13 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>7</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -906,19 +894,19 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -948,7 +936,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -995,19 +983,19 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1037,10 +1025,10 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1084,19 +1072,19 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1126,7 +1114,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1173,19 +1161,19 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1215,13 +1203,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>8</v>
@@ -1262,19 +1250,19 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1304,13 +1292,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1351,19 +1339,19 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1440,19 +1428,19 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1485,7 +1473,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1529,19 +1517,19 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1571,13 +1559,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>10</v>
@@ -1618,19 +1606,19 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1663,7 +1651,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1672,7 +1660,7 @@
         <v>10</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1707,19 +1695,19 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1749,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1761,7 +1749,7 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1796,19 +1784,19 @@
         <v>4</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1885,19 +1873,19 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1927,19 +1915,19 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z16">
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>10</v>
@@ -1974,19 +1962,19 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2016,7 +2004,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2028,7 +2016,7 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>10</v>
@@ -2063,19 +2051,19 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2105,7 +2093,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2117,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>10</v>
@@ -2152,19 +2140,19 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2194,10 +2182,10 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2241,19 +2229,19 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2283,13 +2271,13 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>8</v>
@@ -2330,19 +2318,19 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2372,10 +2360,10 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2419,19 +2407,19 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2461,10 +2449,10 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2473,7 +2461,7 @@
         <v>10</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2508,19 +2496,19 @@
         <v>4</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2597,19 +2585,19 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2686,19 +2674,19 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2728,13 +2716,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>8</v>
@@ -2775,19 +2763,19 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2817,13 +2805,13 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>7</v>
@@ -2864,19 +2852,19 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2909,7 +2897,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2953,19 +2941,19 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3001,7 +2989,7 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -3042,19 +3030,19 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3084,19 +3072,19 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB29">
         <v>5</v>
@@ -3131,19 +3119,19 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3173,7 +3161,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3345,7 +3333,7 @@
         <v>80</v>
       </c>
       <c r="J4">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="K4">
         <v>90</v>
@@ -3354,7 +3342,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>90.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N4">
         <v>87.5</v>
@@ -3366,7 +3354,7 @@
         <v>80</v>
       </c>
       <c r="Q4">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="R4">
         <v>90</v>
@@ -3375,7 +3363,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U4">
         <v>87.5</v>
@@ -3416,13 +3404,13 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N5">
         <v>93.8</v>
@@ -3437,13 +3425,13 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S5">
         <v>100</v>
       </c>
       <c r="T5">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U5">
         <v>93.8</v>
@@ -3478,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3490,7 +3478,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>90.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N6">
         <v>93.8</v>
@@ -3499,7 +3487,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3511,7 +3499,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>90.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U6">
         <v>93.8</v>
@@ -3546,7 +3534,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3558,7 +3546,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -3567,7 +3555,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3579,7 +3567,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -3614,7 +3602,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3626,7 +3614,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -3635,7 +3623,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3647,7 +3635,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -3682,19 +3670,19 @@
         <v>85</v>
       </c>
       <c r="I9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J9">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
-        <v>90.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="N9">
         <v>87.5</v>
@@ -3703,19 +3691,19 @@
         <v>85</v>
       </c>
       <c r="P9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q9">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>90.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="U9">
         <v>87.5</v>
@@ -3750,19 +3738,19 @@
         <v>80</v>
       </c>
       <c r="I10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J10">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="K10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
-        <v>72.7</v>
+        <v>76.2</v>
       </c>
       <c r="N10">
         <v>81.3</v>
@@ -3771,19 +3759,19 @@
         <v>80</v>
       </c>
       <c r="P10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q10">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="R10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S10">
         <v>100</v>
       </c>
       <c r="T10">
-        <v>72.7</v>
+        <v>76.2</v>
       </c>
       <c r="U10">
         <v>81.3</v>
@@ -3824,13 +3812,13 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>90.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N11">
         <v>93.8</v>
@@ -3845,13 +3833,13 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>90.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U11">
         <v>93.8</v>
@@ -3886,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3898,7 +3886,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N12">
         <v>93.8</v>
@@ -3907,7 +3895,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3919,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U12">
         <v>93.8</v>
@@ -3966,7 +3954,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N13">
         <v>87.5</v>
@@ -3987,7 +3975,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U13">
         <v>87.5</v>
@@ -4090,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4111,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -4158,7 +4146,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4170,7 +4158,7 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N16">
         <v>93.8</v>
@@ -4179,7 +4167,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4191,7 +4179,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U16">
         <v>93.8</v>
@@ -4226,7 +4214,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4238,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N17">
         <v>87.5</v>
@@ -4247,7 +4235,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4259,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U17">
         <v>87.5</v>
@@ -4294,19 +4282,19 @@
         <v>85</v>
       </c>
       <c r="I18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4315,19 +4303,19 @@
         <v>85</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -4365,16 +4353,16 @@
         <v>80</v>
       </c>
       <c r="J19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="K19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="N19">
         <v>93.8</v>
@@ -4386,16 +4374,16 @@
         <v>80</v>
       </c>
       <c r="Q19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="U19">
         <v>93.8</v>
@@ -4433,16 +4421,16 @@
         <v>80</v>
       </c>
       <c r="J20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>90.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="N20">
         <v>81.3</v>
@@ -4454,16 +4442,16 @@
         <v>80</v>
       </c>
       <c r="Q20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>90.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="U20">
         <v>81.3</v>
@@ -4504,13 +4492,13 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
-        <v>90.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="N21">
         <v>93.8</v>
@@ -4525,13 +4513,13 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S21">
         <v>100</v>
       </c>
       <c r="T21">
-        <v>90.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="U21">
         <v>93.8</v>
@@ -4566,7 +4554,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4578,7 +4566,7 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N22">
         <v>93.8</v>
@@ -4587,7 +4575,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4599,7 +4587,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U22">
         <v>93.8</v>
@@ -4634,19 +4622,19 @@
         <v>95</v>
       </c>
       <c r="I23">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="K23">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>72.7</v>
+        <v>61.9</v>
       </c>
       <c r="N23">
         <v>81.3</v>
@@ -4655,19 +4643,19 @@
         <v>95</v>
       </c>
       <c r="P23">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="R23">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="S23">
         <v>100</v>
       </c>
       <c r="T23">
-        <v>72.7</v>
+        <v>61.9</v>
       </c>
       <c r="U23">
         <v>81.3</v>
@@ -4702,19 +4690,19 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>72.7</v>
+        <v>76.2</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -4723,19 +4711,19 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S24">
         <v>100</v>
       </c>
       <c r="T24">
-        <v>72.7</v>
+        <v>76.2</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -4770,7 +4758,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4782,7 +4770,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -4791,7 +4779,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4803,7 +4791,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -4838,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4850,7 +4838,7 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4859,7 +4847,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4871,7 +4859,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -4912,13 +4900,13 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="N27">
         <v>93.8</v>
@@ -4933,13 +4921,13 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U27">
         <v>93.8</v>
@@ -4977,16 +4965,16 @@
         <v>90</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4998,16 +4986,16 @@
         <v>90</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5042,19 +5030,19 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -5063,19 +5051,19 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -5110,7 +5098,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5122,7 +5110,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>72.7</v>
+        <v>83.3</v>
       </c>
       <c r="N30">
         <v>93.8</v>
@@ -5131,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5143,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>72.7</v>
+        <v>83.3</v>
       </c>
       <c r="U30">
         <v>93.8</v>
@@ -5215,19 +5203,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2">
-        <v>44.4</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2">
-        <v>55.6</v>
+        <v>63</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5238,7 +5226,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -5270,7 +5258,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -5279,19 +5267,19 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>70.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="G4" s="2">
-        <v>29.6</v>
+        <v>33.3</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5302,7 +5290,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5311,19 +5299,19 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>77.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>22.2</v>
+        <v>25.9</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5334,7 +5322,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -5343,19 +5331,19 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
       <c r="G6" s="2">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5433,7 +5421,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -5489,7 +5477,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5521,7 +5509,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920015</v>
+        <v>23330051920018</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -5530,10 +5518,10 @@
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
@@ -5544,7 +5532,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920015</v>
+        <v>23330051920018</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -5553,7 +5541,7 @@
         <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5567,19 +5555,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920017</v>
+        <v>23330051920024</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -5590,22 +5578,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920017</v>
+        <v>23330051920024</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5613,19 +5601,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920022</v>
+        <v>23330051920003</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -5636,16 +5624,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920022</v>
+        <v>23330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5659,16 +5647,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920005</v>
+        <v>23330051920008</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5682,16 +5670,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920008</v>
+        <v>23330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5705,16 +5693,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920009</v>
+        <v>23330051920021</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5728,16 +5716,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920016</v>
+        <v>23330051920020</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
         <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5746,75 +5734,6 @@
         <v>53</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920021</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920020</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920023</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20231.xlsx
+++ b/grupos/1AM - Estadisticos 20231.xlsx
@@ -188,13 +188,13 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
@@ -814,16 +814,16 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -856,13 +856,13 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -903,16 +903,16 @@
         <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -954,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -992,16 +992,16 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1034,7 +1034,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1043,7 +1043,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1081,16 +1081,16 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1170,16 +1170,16 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1218,10 +1218,10 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1259,16 +1259,16 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1301,7 +1301,7 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA9">
         <v>5</v>
@@ -1348,16 +1348,16 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1390,13 +1390,13 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1437,16 +1437,16 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1479,7 +1479,7 @@
         <v>6</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1488,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1526,16 +1526,16 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1615,16 +1615,16 @@
         <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1704,16 +1704,16 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1793,16 +1793,16 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1882,16 +1882,16 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1930,7 +1930,7 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -1971,16 +1971,16 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2022,7 +2022,7 @@
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2060,16 +2060,16 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2149,16 +2149,16 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2191,16 +2191,16 @@
         <v>5</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2238,16 +2238,16 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2280,16 +2280,16 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2327,16 +2327,16 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2369,13 +2369,13 @@
         <v>5</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2416,16 +2416,16 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2458,16 +2458,16 @@
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2505,16 +2505,16 @@
         <v>2</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2547,7 +2547,7 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2594,16 +2594,16 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2636,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2645,7 +2645,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2683,16 +2683,16 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2725,7 +2725,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2772,16 +2772,16 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2820,10 +2820,10 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2861,16 +2861,16 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2903,16 +2903,16 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2950,16 +2950,16 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2992,13 +2992,13 @@
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3039,16 +3039,16 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3128,16 +3128,16 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3170,16 +3170,16 @@
         <v>5</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>5</v>
       </c>
       <c r="AB30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3345,10 +3345,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N4">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P4">
         <v>80</v>
@@ -3366,10 +3366,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U4">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V4">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3413,7 +3413,7 @@
         <v>95.2</v>
       </c>
       <c r="N5">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3434,7 +3434,7 @@
         <v>95.2</v>
       </c>
       <c r="U5">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3481,10 +3481,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P6">
         <v>90</v>
@@ -3502,10 +3502,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3685,10 +3685,10 @@
         <v>85.7</v>
       </c>
       <c r="N9">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O9">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P9">
         <v>85</v>
@@ -3706,10 +3706,10 @@
         <v>85.7</v>
       </c>
       <c r="U9">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V9">
-        <v>85</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3747,7 +3747,7 @@
         <v>90</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="M10">
         <v>76.2</v>
@@ -3756,7 +3756,7 @@
         <v>81.3</v>
       </c>
       <c r="O10">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="P10">
         <v>90</v>
@@ -3768,7 +3768,7 @@
         <v>90</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="T10">
         <v>76.2</v>
@@ -3777,7 +3777,7 @@
         <v>81.3</v>
       </c>
       <c r="V10">
-        <v>80</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3821,10 +3821,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P11">
         <v>80</v>
@@ -3842,10 +3842,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3889,7 +3889,7 @@
         <v>95.2</v>
       </c>
       <c r="N12">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3910,7 +3910,7 @@
         <v>95.2</v>
       </c>
       <c r="U12">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -3957,10 +3957,10 @@
         <v>95.2</v>
       </c>
       <c r="N13">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P13">
         <v>90</v>
@@ -3978,10 +3978,10 @@
         <v>95.2</v>
       </c>
       <c r="U13">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V13">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4028,7 +4028,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4049,7 +4049,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4161,7 +4161,7 @@
         <v>95.2</v>
       </c>
       <c r="N16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4182,7 +4182,7 @@
         <v>95.2</v>
       </c>
       <c r="U16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4229,7 +4229,7 @@
         <v>95.2</v>
       </c>
       <c r="N17">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4250,7 +4250,7 @@
         <v>95.2</v>
       </c>
       <c r="U17">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4300,7 +4300,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="P18">
         <v>95</v>
@@ -4321,7 +4321,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4365,10 +4365,10 @@
         <v>35.7</v>
       </c>
       <c r="N19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="P19">
         <v>80</v>
@@ -4386,10 +4386,10 @@
         <v>35.7</v>
       </c>
       <c r="U19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V19">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4433,10 +4433,10 @@
         <v>85.7</v>
       </c>
       <c r="N20">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O20">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P20">
         <v>80</v>
@@ -4454,10 +4454,10 @@
         <v>85.7</v>
       </c>
       <c r="U20">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V20">
-        <v>85</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4501,10 +4501,10 @@
         <v>85.7</v>
       </c>
       <c r="N21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O21">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="P21">
         <v>80</v>
@@ -4522,10 +4522,10 @@
         <v>85.7</v>
       </c>
       <c r="U21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V21">
-        <v>90</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4569,7 +4569,7 @@
         <v>95.2</v>
       </c>
       <c r="N22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4590,7 +4590,7 @@
         <v>95.2</v>
       </c>
       <c r="U22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4631,16 +4631,16 @@
         <v>65</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="M23">
         <v>61.9</v>
       </c>
       <c r="N23">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O23">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="P23">
         <v>40</v>
@@ -4652,16 +4652,16 @@
         <v>65</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="T23">
         <v>61.9</v>
       </c>
       <c r="U23">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="V23">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4705,10 +4705,10 @@
         <v>76.2</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P24">
         <v>85</v>
@@ -4726,10 +4726,10 @@
         <v>76.2</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4909,7 +4909,7 @@
         <v>90.5</v>
       </c>
       <c r="N27">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -4930,7 +4930,7 @@
         <v>90.5</v>
       </c>
       <c r="U27">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5113,7 +5113,7 @@
         <v>83.3</v>
       </c>
       <c r="N30">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5134,7 +5134,7 @@
         <v>83.3</v>
       </c>
       <c r="U30">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5299,19 +5299,19 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2">
-        <v>74.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="G5" s="2">
-        <v>25.9</v>
+        <v>33.3</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -5331,19 +5331,19 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>77.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>22.2</v>
+        <v>25.9</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5354,7 +5354,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -5363,19 +5363,19 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>81.5</v>
+        <v>85.2</v>
       </c>
       <c r="G7" s="2">
-        <v>18.5</v>
+        <v>14.8</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5395,19 +5395,19 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>92.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="G8" s="2">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5593,7 +5593,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>

--- a/grupos/1AM - Estadisticos 20231.xlsx
+++ b/grupos/1AM - Estadisticos 20231.xlsx
@@ -1161,7 +1161,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -1203,7 +1203,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>7</v>

--- a/grupos/1AM - Estadisticos 20231.xlsx
+++ b/grupos/1AM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -188,15 +188,15 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -212,22 +212,25 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
   </si>
   <si>
     <t>SANTOS</t>
@@ -236,34 +239,37 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>UTRERA</t>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
-  </si>
-  <si>
-    <t>ERICK ANGEL</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
   </si>
   <si>
     <t>OMAR DAVID</t>
@@ -272,13 +278,19 @@
     <t>JUAN SEBASTIAN</t>
   </si>
   <si>
-    <t>JAIME</t>
+    <t>JUAN YAHEL</t>
+  </si>
+  <si>
+    <t>HERSON</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -826,43 +838,43 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -915,25 +927,25 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1004,46 +1016,46 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1093,25 +1105,25 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1182,25 +1194,25 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1212,13 +1224,13 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1271,25 +1283,25 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1301,16 +1313,16 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>5</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1360,25 +1372,25 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1390,13 +1402,13 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1449,25 +1461,25 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1476,7 +1488,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -1485,10 +1497,10 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1538,31 +1550,31 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1571,10 +1583,10 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>7</v>
@@ -1627,25 +1639,25 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1716,25 +1728,25 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1746,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1805,25 +1817,25 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1894,31 +1906,31 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1983,25 +1995,25 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2010,16 +2022,16 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2072,40 +2084,40 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>10</v>
@@ -2161,34 +2173,34 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2197,10 +2209,10 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2250,28 +2262,28 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2283,13 +2295,13 @@
         <v>7</v>
       </c>
       <c r="AA20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2339,43 +2351,43 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>5</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2428,28 +2440,28 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2464,7 +2476,7 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC22">
         <v>7</v>
@@ -2517,25 +2529,25 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2547,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2606,25 +2618,25 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2645,7 +2657,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2695,31 +2707,31 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2734,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2784,34 +2796,34 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>7</v>
@@ -2820,10 +2832,10 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2873,46 +2885,46 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2962,43 +2974,43 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3051,34 +3063,34 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>8</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3087,10 +3099,10 @@
         <v>9</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3140,34 +3152,34 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -3176,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3351,25 +3363,25 @@
         <v>90</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R4">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>92.90000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="U4">
-        <v>93.8</v>
+        <v>68.8</v>
       </c>
       <c r="V4">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3425,16 +3437,16 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
       </c>
       <c r="T5">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="U5">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3487,7 +3499,7 @@
         <v>97.5</v>
       </c>
       <c r="P6">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3499,13 +3511,13 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>92.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="U6">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3555,7 +3567,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3567,7 +3579,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -3623,7 +3635,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3635,10 +3647,10 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3691,25 +3703,25 @@
         <v>92.5</v>
       </c>
       <c r="P9">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="Q9">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>85.7</v>
+        <v>88.5</v>
       </c>
       <c r="U9">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="V9">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3759,25 +3771,25 @@
         <v>82.5</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q10">
-        <v>86.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R10">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S10">
-        <v>81.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T10">
-        <v>76.2</v>
+        <v>82</v>
       </c>
       <c r="U10">
-        <v>81.3</v>
+        <v>79.2</v>
       </c>
       <c r="V10">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3827,25 +3839,25 @@
         <v>92.5</v>
       </c>
       <c r="P11">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>92.90000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="U11">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V11">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3895,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3907,10 +3919,10 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="U12">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -3966,7 +3978,7 @@
         <v>90</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3975,13 +3987,13 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="U13">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4049,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4099,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -4167,7 +4179,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4179,10 +4191,10 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="U16">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4235,10 +4247,10 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4247,10 +4259,10 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="U17">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4303,25 +4315,25 @@
         <v>90</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>90.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4374,22 +4386,22 @@
         <v>80</v>
       </c>
       <c r="Q19">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R19">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>35.7</v>
+        <v>50.8</v>
       </c>
       <c r="U19">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4439,25 +4451,25 @@
         <v>87.5</v>
       </c>
       <c r="P20">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q20">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R20">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>85.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="U20">
-        <v>84.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V20">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4507,25 +4519,25 @@
         <v>92.5</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R21">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S21">
         <v>100</v>
       </c>
       <c r="T21">
-        <v>85.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="U21">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V21">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4575,10 +4587,10 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4587,10 +4599,10 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U22">
-        <v>96.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4643,25 +4655,25 @@
         <v>80</v>
       </c>
       <c r="P23">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="Q23">
-        <v>86.7</v>
+        <v>66.7</v>
       </c>
       <c r="R23">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="S23">
-        <v>81.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="T23">
-        <v>61.9</v>
+        <v>47.5</v>
       </c>
       <c r="U23">
-        <v>71.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="V23">
-        <v>80</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4711,25 +4723,25 @@
         <v>97.5</v>
       </c>
       <c r="P24">
-        <v>85</v>
+        <v>63.3</v>
       </c>
       <c r="Q24">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="S24">
         <v>100</v>
       </c>
       <c r="T24">
-        <v>76.2</v>
+        <v>82</v>
       </c>
       <c r="U24">
-        <v>96.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="V24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4779,7 +4791,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4791,7 +4803,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -4859,10 +4871,10 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>90.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -4915,22 +4927,22 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="U27">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -4983,22 +4995,22 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q28">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="R28">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5051,19 +5063,19 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -5119,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5131,10 +5143,10 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>83.3</v>
+        <v>90.2</v>
       </c>
       <c r="U30">
-        <v>96.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5203,19 +5215,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>37</v>
+        <v>48.1</v>
       </c>
       <c r="G2" s="2">
-        <v>63</v>
+        <v>51.9</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5235,16 +5247,16 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>55.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>44.4</v>
+        <v>29.6</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -5267,19 +5279,19 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>25.9</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5290,7 +5302,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5299,19 +5311,19 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="G5" s="2">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5331,16 +5343,16 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>74.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="G6" s="2">
-        <v>25.9</v>
+        <v>18.5</v>
       </c>
       <c r="H6">
         <v>7.4</v>
@@ -5354,7 +5366,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -5375,7 +5387,7 @@
         <v>14.8</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5395,19 +5407,19 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>96.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>3.7</v>
+        <v>11.1</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5477,7 +5489,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5509,16 +5521,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920018</v>
+        <v>23330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5532,16 +5544,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920018</v>
+        <v>23330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5555,22 +5567,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920024</v>
+        <v>23330051920017</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5578,22 +5590,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920024</v>
+        <v>23330051920017</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5601,16 +5613,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920003</v>
+        <v>23330051920025</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5624,16 +5636,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920005</v>
+        <v>23330051920025</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5647,16 +5659,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920008</v>
+        <v>23330051920005</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5670,16 +5682,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920009</v>
+        <v>23330051920008</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5693,16 +5705,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920021</v>
+        <v>23330051920015</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5716,24 +5728,93 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920020</v>
+        <v>23330051920016</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920021</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
         <v>53</v>
       </c>
-      <c r="G11">
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920020</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920022</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20231.xlsx
+++ b/grupos/1AM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -174,9 +177,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
@@ -652,13 +652,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AG30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -669,35 +669,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,77 +727,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -823,43 +839,43 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>5</v>
       </c>
       <c r="N4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>5</v>
       </c>
       <c r="R4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -871,18 +887,30 @@
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB4">
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD4">
+        <v>6</v>
+      </c>
+      <c r="AE4">
+        <v>5</v>
+      </c>
+      <c r="AF4">
+        <v>5</v>
+      </c>
+      <c r="AG4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>9</v>
@@ -909,69 +937,81 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
       </c>
       <c r="S5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>7</v>
+      </c>
+      <c r="AE5">
+        <v>10</v>
+      </c>
+      <c r="AF5">
+        <v>8</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -998,69 +1038,81 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z6">
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD6">
+        <v>7</v>
+      </c>
+      <c r="AE6">
+        <v>9</v>
+      </c>
+      <c r="AF6">
+        <v>7</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -1087,19 +1139,19 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>8</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1108,48 +1160,60 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
       </c>
       <c r="S7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z7">
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7">
+        <v>7</v>
+      </c>
+      <c r="AE7">
+        <v>10</v>
+      </c>
+      <c r="AF7">
+        <v>10</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1173,72 +1237,84 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>8</v>
       </c>
       <c r="P8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z8">
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>8</v>
+      </c>
+      <c r="AF8">
+        <v>8</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -1262,72 +1338,84 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>5</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD9">
+        <v>5</v>
+      </c>
+      <c r="AE9">
+        <v>8</v>
+      </c>
+      <c r="AF9">
+        <v>6</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -1351,16 +1439,16 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1372,7 +1460,7 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -1384,7 +1472,7 @@
         <v>5</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1413,10 +1501,22 @@
       <c r="AC10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10">
+        <v>5</v>
+      </c>
+      <c r="AE10">
+        <v>5</v>
+      </c>
+      <c r="AF10">
+        <v>5</v>
+      </c>
+      <c r="AG10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -1440,72 +1540,84 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD11">
+        <v>5</v>
+      </c>
+      <c r="AE11">
+        <v>7</v>
+      </c>
+      <c r="AF11">
+        <v>7</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1532,55 +1644,55 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>10</v>
       </c>
       <c r="S12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>6</v>
@@ -1589,12 +1701,24 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD12">
+        <v>6</v>
+      </c>
+      <c r="AE12">
+        <v>8</v>
+      </c>
+      <c r="AF12">
+        <v>7</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -1618,72 +1742,84 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>8</v>
       </c>
       <c r="K13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>10</v>
       </c>
       <c r="P13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13">
+        <v>7</v>
+      </c>
+      <c r="AE13">
+        <v>10</v>
+      </c>
+      <c r="AF13">
+        <v>10</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1710,19 +1846,19 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>9</v>
       </c>
       <c r="L14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1731,22 +1867,22 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1758,21 +1894,33 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD14">
+        <v>8</v>
+      </c>
+      <c r="AE14">
+        <v>10</v>
+      </c>
+      <c r="AF14">
+        <v>10</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1814,17 +1962,17 @@
         <v>5</v>
       </c>
       <c r="O15">
+        <v>5</v>
+      </c>
+      <c r="P15">
         <v>0</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>5</v>
+      </c>
+      <c r="R15">
         <v>3</v>
       </c>
-      <c r="Q15">
-        <v>5</v>
-      </c>
-      <c r="R15">
-        <v>5</v>
-      </c>
       <c r="S15">
         <v>5</v>
       </c>
@@ -1835,14 +1983,14 @@
         <v>5</v>
       </c>
       <c r="V15">
+        <v>5</v>
+      </c>
+      <c r="W15">
+        <v>5</v>
+      </c>
+      <c r="X15">
         <v>0</v>
       </c>
-      <c r="W15">
-        <v>5</v>
-      </c>
-      <c r="X15">
-        <v>5</v>
-      </c>
       <c r="Y15">
         <v>5</v>
       </c>
@@ -1858,10 +2006,22 @@
       <c r="AC15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>5</v>
+      </c>
+      <c r="AF15">
+        <v>5</v>
+      </c>
+      <c r="AG15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -1888,55 +2048,55 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
       </c>
       <c r="S16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -1947,10 +2107,22 @@
       <c r="AC16">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:29">
+      <c r="AD16">
+        <v>7</v>
+      </c>
+      <c r="AE16">
+        <v>9</v>
+      </c>
+      <c r="AF16">
+        <v>10</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>8</v>
@@ -1977,28 +2149,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -2007,22 +2179,22 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17">
         <v>9</v>
@@ -2031,15 +2203,27 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD17">
+        <v>7</v>
+      </c>
+      <c r="AE17">
+        <v>9</v>
+      </c>
+      <c r="AF17">
+        <v>8</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>8</v>
@@ -2066,69 +2250,81 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>7</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD18">
+        <v>7</v>
+      </c>
+      <c r="AE18">
+        <v>10</v>
+      </c>
+      <c r="AF18">
+        <v>9</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -2152,19 +2348,19 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>5</v>
@@ -2173,51 +2369,63 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>7</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>6</v>
       </c>
       <c r="AC19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD19">
+        <v>5</v>
+      </c>
+      <c r="AE19">
+        <v>6</v>
+      </c>
+      <c r="AF19">
+        <v>6</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>6</v>
@@ -2241,13 +2449,13 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2262,22 +2470,22 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2286,27 +2494,39 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>6</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC20">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD20">
+        <v>6</v>
+      </c>
+      <c r="AE20">
+        <v>6</v>
+      </c>
+      <c r="AF20">
+        <v>6</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -2333,34 +2553,34 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P21">
+        <v>6</v>
+      </c>
+      <c r="Q21">
+        <v>10</v>
+      </c>
+      <c r="R21">
         <v>3</v>
       </c>
-      <c r="Q21">
-        <v>7</v>
-      </c>
-      <c r="R21">
-        <v>5</v>
-      </c>
       <c r="S21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2369,33 +2589,45 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD21">
+        <v>5</v>
+      </c>
+      <c r="AE21">
+        <v>6</v>
+      </c>
+      <c r="AF21">
+        <v>6</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>6</v>
@@ -2419,72 +2651,84 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>6</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>10</v>
+      </c>
+      <c r="R22">
         <v>3</v>
       </c>
-      <c r="Q22">
-        <v>5</v>
-      </c>
-      <c r="R22">
-        <v>6</v>
-      </c>
       <c r="S22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA22">
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD22">
+        <v>5</v>
+      </c>
+      <c r="AE22">
+        <v>5</v>
+      </c>
+      <c r="AF22">
+        <v>7</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -2514,13 +2758,13 @@
         <v>5</v>
       </c>
       <c r="K23">
+        <v>5</v>
+      </c>
+      <c r="L23">
         <v>2</v>
       </c>
-      <c r="L23">
-        <v>7</v>
-      </c>
       <c r="M23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>5</v>
@@ -2529,20 +2773,20 @@
         <v>5</v>
       </c>
       <c r="P23">
+        <v>5</v>
+      </c>
+      <c r="Q23">
+        <v>5</v>
+      </c>
+      <c r="R23">
         <v>3</v>
       </c>
-      <c r="Q23">
-        <v>5</v>
-      </c>
-      <c r="R23">
+      <c r="S23">
+        <v>5</v>
+      </c>
+      <c r="T23">
         <v>1</v>
       </c>
-      <c r="S23">
-        <v>5</v>
-      </c>
-      <c r="T23">
-        <v>5</v>
-      </c>
       <c r="U23">
         <v>5</v>
       </c>
@@ -2570,10 +2814,22 @@
       <c r="AC23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:29">
+      <c r="AD23">
+        <v>5</v>
+      </c>
+      <c r="AE23">
+        <v>5</v>
+      </c>
+      <c r="AF23">
+        <v>5</v>
+      </c>
+      <c r="AG23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -2597,58 +2853,58 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>6</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>5</v>
       </c>
       <c r="P24">
+        <v>5</v>
+      </c>
+      <c r="Q24">
+        <v>10</v>
+      </c>
+      <c r="R24">
         <v>3</v>
       </c>
-      <c r="Q24">
-        <v>5</v>
-      </c>
-      <c r="R24">
+      <c r="S24">
+        <v>5</v>
+      </c>
+      <c r="T24">
         <v>4</v>
       </c>
-      <c r="S24">
-        <v>7</v>
-      </c>
-      <c r="T24">
-        <v>5</v>
-      </c>
       <c r="U24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>5</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2657,12 +2913,24 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD24">
+        <v>5</v>
+      </c>
+      <c r="AE24">
+        <v>5</v>
+      </c>
+      <c r="AF24">
+        <v>6</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -2689,19 +2957,19 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>8</v>
       </c>
       <c r="L25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2710,48 +2978,60 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z25">
         <v>9</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:29">
+      <c r="AD25">
+        <v>5</v>
+      </c>
+      <c r="AE25">
+        <v>10</v>
+      </c>
+      <c r="AF25">
+        <v>9</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -2778,58 +3058,58 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>7</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>6</v>
       </c>
       <c r="S26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>6</v>
@@ -2837,10 +3117,22 @@
       <c r="AC26">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:29">
+      <c r="AD26">
+        <v>5</v>
+      </c>
+      <c r="AE26">
+        <v>6</v>
+      </c>
+      <c r="AF26">
+        <v>7</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>7</v>
@@ -2864,19 +3156,19 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>5</v>
@@ -2885,51 +3177,63 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD27">
+        <v>5</v>
+      </c>
+      <c r="AE27">
+        <v>7</v>
+      </c>
+      <c r="AF27">
+        <v>6</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>7</v>
@@ -2953,58 +3257,58 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>7</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>6</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>5</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>6</v>
@@ -3013,12 +3317,24 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD28">
+        <v>6</v>
+      </c>
+      <c r="AE28">
+        <v>7</v>
+      </c>
+      <c r="AF28">
+        <v>7</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>6</v>
@@ -3045,69 +3361,81 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>10</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>7</v>
       </c>
       <c r="AC29">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD29">
+        <v>9</v>
+      </c>
+      <c r="AE29">
+        <v>7</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -3134,52 +3462,52 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -3191,15 +3519,27 @@
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="AD30">
+        <v>5</v>
+      </c>
+      <c r="AE30">
+        <v>7</v>
+      </c>
+      <c r="AF30">
+        <v>8</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3207,16 +3547,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3224,26 +3564,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3269,56 +3612,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>80</v>
@@ -3342,51 +3694,60 @@
         <v>95</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>80</v>
-      </c>
-      <c r="J4">
-        <v>90</v>
       </c>
       <c r="K4">
         <v>90</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
         <v>92.90000000000001</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>93.8</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>90</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>81.3</v>
+      </c>
+      <c r="R4">
         <v>86.7</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>93.8</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>84.40000000000001</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
         <v>93.40000000000001</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>68.8</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>90.59999999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Y4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -3416,20 +3777,20 @@
         <v>100</v>
       </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>95</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
       <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
         <v>95.2</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>96.90000000000001</v>
       </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
       <c r="P5">
         <v>100</v>
       </c>
@@ -3437,24 +3798,33 @@
         <v>100</v>
       </c>
       <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>96.90000000000001</v>
       </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5">
         <v>95.09999999999999</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>97.90000000000001</v>
       </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>80</v>
@@ -3478,11 +3848,11 @@
         <v>100</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
         <v>100</v>
       </c>
@@ -3490,39 +3860,48 @@
         <v>100</v>
       </c>
       <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
         <v>92.90000000000001</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>96.90000000000001</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>97.5</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>93.3</v>
       </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
-        <v>100</v>
-      </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
         <v>96.7</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>97.90000000000001</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>80</v>
@@ -3546,11 +3925,11 @@
         <v>100</v>
       </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>90</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
         <v>100</v>
       </c>
@@ -3558,39 +3937,48 @@
         <v>100</v>
       </c>
       <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
         <v>95.2</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>93.3</v>
       </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
-        <v>100</v>
-      </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
         <v>98.40000000000001</v>
       </c>
-      <c r="U7">
-        <v>100</v>
-      </c>
-      <c r="V7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7">
+        <v>100</v>
+      </c>
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>80</v>
@@ -3614,11 +4002,11 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>85</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
         <v>100</v>
       </c>
@@ -3626,39 +4014,48 @@
         <v>100</v>
       </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
         <v>95.2</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>86.7</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
-        <v>100</v>
-      </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>98.40000000000001</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>95.8</v>
       </c>
-      <c r="V8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -3682,51 +4079,60 @@
         <v>85</v>
       </c>
       <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
         <v>85</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>90</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>95</v>
       </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
       <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
         <v>85.7</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>93.8</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>92.5</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>86.7</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>91.7</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>95.3</v>
       </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
         <v>88.5</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>91.7</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>80</v>
@@ -3750,51 +4156,60 @@
         <v>80</v>
       </c>
       <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
         <v>90</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>86.7</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>90</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>81.5</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>76.2</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>81.3</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>82.5</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
+        <v>81.3</v>
+      </c>
+      <c r="R10">
         <v>86.7</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>72.90000000000001</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>92.2</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>88.90000000000001</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>82</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>79.2</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>85.90000000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="Y10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>80</v>
@@ -3818,51 +4233,60 @@
         <v>100</v>
       </c>
       <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
         <v>80</v>
       </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>95</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
         <v>92.90000000000001</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>96.90000000000001</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>92.5</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>86.7</v>
       </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
-      <c r="R11">
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>96.90000000000001</v>
       </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11">
         <v>93.40000000000001</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>93.8</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>80</v>
@@ -3886,11 +4310,11 @@
         <v>100</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>90</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
         <v>100</v>
       </c>
@@ -3898,39 +4322,48 @@
         <v>100</v>
       </c>
       <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12">
         <v>95.2</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>96.90000000000001</v>
       </c>
-      <c r="O12">
-        <v>100</v>
-      </c>
       <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>93.3</v>
       </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
-        <v>100</v>
-      </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
         <v>96.7</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>93.8</v>
       </c>
-      <c r="V12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="X12">
+        <v>100</v>
+      </c>
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>90</v>
@@ -3954,11 +4387,11 @@
         <v>90</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>90</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
         <v>100</v>
       </c>
@@ -3966,39 +4399,48 @@
         <v>100</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
         <v>95.2</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>93.8</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>95</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>90</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>97.90000000000001</v>
       </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
       <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
         <v>96.7</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>95.8</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4040,11 +4482,11 @@
         <v>100</v>
       </c>
       <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
         <v>95</v>
       </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
       <c r="Q14">
         <v>100</v>
       </c>
@@ -4061,12 +4503,21 @@
         <v>100</v>
       </c>
       <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
+        <v>100</v>
+      </c>
+      <c r="X14">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>80</v>
@@ -4090,10 +4541,10 @@
         <v>0</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>40</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -4111,13 +4562,13 @@
         <v>0</v>
       </c>
       <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>50</v>
+      </c>
+      <c r="R15">
         <v>26.7</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4131,10 +4582,19 @@
       <c r="V15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>90</v>
@@ -4158,11 +4618,11 @@
         <v>100</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>95</v>
       </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
       <c r="K16">
         <v>100</v>
       </c>
@@ -4170,39 +4630,48 @@
         <v>100</v>
       </c>
       <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
         <v>95.2</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>96.90000000000001</v>
       </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>96.7</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
-        <v>100</v>
-      </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
         <v>96.7</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>97.90000000000001</v>
       </c>
-      <c r="V16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="X16">
+        <v>100</v>
+      </c>
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>90</v>
@@ -4226,11 +4695,11 @@
         <v>100</v>
       </c>
       <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
         <v>95</v>
       </c>
-      <c r="J17">
-        <v>100</v>
-      </c>
       <c r="K17">
         <v>100</v>
       </c>
@@ -4238,39 +4707,48 @@
         <v>100</v>
       </c>
       <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
         <v>95.2</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>93.8</v>
       </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
       <c r="P17">
+        <v>100</v>
+      </c>
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>93.3</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>97.90000000000001</v>
       </c>
-      <c r="R17">
-        <v>100</v>
-      </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
       <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
         <v>96.7</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>95.8</v>
       </c>
-      <c r="V17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="X17">
+        <v>100</v>
+      </c>
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>90</v>
@@ -4294,51 +4772,60 @@
         <v>85</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>95</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>95</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
         <v>90.5</v>
       </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
       <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
         <v>90</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>93.3</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>96.90000000000001</v>
       </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
         <v>95.09999999999999</v>
       </c>
-      <c r="U18">
-        <v>100</v>
-      </c>
-      <c r="V18">
+      <c r="W18">
+        <v>100</v>
+      </c>
+      <c r="X18">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -4362,51 +4849,60 @@
         <v>85</v>
       </c>
       <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
         <v>80</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>96.7</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>90</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
       <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
         <v>35.7</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>96.90000000000001</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>90</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>80</v>
       </c>
-      <c r="Q19">
+      <c r="S19">
         <v>97.90000000000001</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>92.2</v>
       </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
+      <c r="U19">
+        <v>100</v>
+      </c>
+      <c r="V19">
         <v>50.8</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>91.7</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>80</v>
@@ -4430,51 +4926,60 @@
         <v>85</v>
       </c>
       <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
         <v>80</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>90</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>85</v>
       </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
       <c r="M20">
+        <v>100</v>
+      </c>
+      <c r="N20">
         <v>85.7</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>84.40000000000001</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>87.5</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>86.7</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>93.8</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>90.59999999999999</v>
       </c>
-      <c r="S20">
-        <v>100</v>
-      </c>
-      <c r="T20">
+      <c r="U20">
+        <v>100</v>
+      </c>
+      <c r="V20">
         <v>86.90000000000001</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>85.40000000000001</v>
       </c>
-      <c r="V20">
+      <c r="X20">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>80</v>
@@ -4498,51 +5003,60 @@
         <v>90</v>
       </c>
       <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
         <v>80</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>95</v>
       </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
       <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
         <v>85.7</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>96.90000000000001</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>92.5</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>83.3</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>97.90000000000001</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>93.8</v>
       </c>
-      <c r="S21">
-        <v>100</v>
-      </c>
-      <c r="T21">
+      <c r="U21">
+        <v>100</v>
+      </c>
+      <c r="V21">
         <v>86.90000000000001</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>93.8</v>
       </c>
-      <c r="V21">
+      <c r="X21">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -4566,11 +5080,11 @@
         <v>100</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>90</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
         <v>100</v>
       </c>
@@ -4578,39 +5092,48 @@
         <v>100</v>
       </c>
       <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
         <v>95.2</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>96.90000000000001</v>
       </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
       <c r="P22">
+        <v>100</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>86.7</v>
       </c>
-      <c r="Q22">
+      <c r="S22">
         <v>97.90000000000001</v>
       </c>
-      <c r="R22">
-        <v>100</v>
-      </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
       <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
         <v>98.40000000000001</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>70.8</v>
       </c>
-      <c r="V22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="X22">
+        <v>100</v>
+      </c>
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>80</v>
@@ -4634,51 +5157,60 @@
         <v>95</v>
       </c>
       <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>40</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>86.7</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>65</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>81.5</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>61.9</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>71.90000000000001</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>80</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
+        <v>81.3</v>
+      </c>
+      <c r="R23">
         <v>33.3</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>66.7</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>75</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>71.09999999999999</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>47.5</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>47.9</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>81.3</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Y23">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -4702,51 +5234,60 @@
         <v>100</v>
       </c>
       <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
         <v>85</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>96.7</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>95</v>
       </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
       <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
         <v>76.2</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>96.90000000000001</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>97.5</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>63.3</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>91.7</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>92.2</v>
       </c>
-      <c r="S24">
-        <v>100</v>
-      </c>
-      <c r="T24">
+      <c r="U24">
+        <v>100</v>
+      </c>
+      <c r="V24">
         <v>82</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>68.8</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -4770,11 +5311,11 @@
         <v>100</v>
       </c>
       <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
         <v>90</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
       <c r="K25">
         <v>100</v>
       </c>
@@ -4782,39 +5323,48 @@
         <v>100</v>
       </c>
       <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
         <v>95.2</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>86.7</v>
       </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
-        <v>100</v>
-      </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
+        <v>100</v>
+      </c>
+      <c r="V25">
         <v>98.40000000000001</v>
       </c>
-      <c r="U25">
-        <v>100</v>
-      </c>
-      <c r="V25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="W25">
+        <v>100</v>
+      </c>
+      <c r="X25">
+        <v>100</v>
+      </c>
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -4838,11 +5388,11 @@
         <v>100</v>
       </c>
       <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
         <v>90</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
       <c r="K26">
         <v>100</v>
       </c>
@@ -4850,39 +5400,48 @@
         <v>100</v>
       </c>
       <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
         <v>90.5</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>90</v>
       </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
-        <v>100</v>
-      </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
+        <v>100</v>
+      </c>
+      <c r="V26">
         <v>95.09999999999999</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>93.8</v>
       </c>
-      <c r="V26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="X26">
+        <v>100</v>
+      </c>
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>90</v>
@@ -4906,51 +5465,60 @@
         <v>100</v>
       </c>
       <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27">
         <v>90</v>
       </c>
-      <c r="J27">
-        <v>100</v>
-      </c>
       <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
         <v>95</v>
       </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
       <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
         <v>90.5</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>87.5</v>
       </c>
-      <c r="O27">
-        <v>100</v>
-      </c>
       <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>93.3</v>
       </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
         <v>96.90000000000001</v>
       </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
-      <c r="T27">
+      <c r="U27">
+        <v>100</v>
+      </c>
+      <c r="V27">
         <v>95.09999999999999</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>85.40000000000001</v>
       </c>
-      <c r="V27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="X27">
+        <v>100</v>
+      </c>
+      <c r="Y27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>90</v>
@@ -4974,51 +5542,60 @@
         <v>100</v>
       </c>
       <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
         <v>90</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>96.7</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>95</v>
       </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
       <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
         <v>95.2</v>
       </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>86.7</v>
       </c>
-      <c r="Q28">
+      <c r="S28">
         <v>95.8</v>
       </c>
-      <c r="R28">
+      <c r="T28">
         <v>96.90000000000001</v>
       </c>
-      <c r="S28">
-        <v>100</v>
-      </c>
-      <c r="T28">
+      <c r="U28">
+        <v>100</v>
+      </c>
+      <c r="V28">
         <v>98.40000000000001</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>87.5</v>
       </c>
-      <c r="V28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="X28">
+        <v>100</v>
+      </c>
+      <c r="Y28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>80</v>
@@ -5042,51 +5619,60 @@
         <v>100</v>
       </c>
       <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
         <v>90</v>
       </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>95</v>
       </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
       <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
         <v>95.2</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>93.3</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>96.90000000000001</v>
       </c>
-      <c r="S29">
-        <v>100</v>
-      </c>
-      <c r="T29">
+      <c r="U29">
+        <v>100</v>
+      </c>
+      <c r="V29">
         <v>98.40000000000001</v>
       </c>
-      <c r="U29">
-        <v>100</v>
-      </c>
-      <c r="V29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="W29">
+        <v>100</v>
+      </c>
+      <c r="X29">
+        <v>100</v>
+      </c>
+      <c r="Y29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>80</v>
@@ -5110,11 +5696,11 @@
         <v>100</v>
       </c>
       <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
         <v>90</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
       <c r="K30">
         <v>100</v>
       </c>
@@ -5122,41 +5708,50 @@
         <v>100</v>
       </c>
       <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
         <v>83.3</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>96.90000000000001</v>
       </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
       <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
         <v>93.3</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
-        <v>100</v>
-      </c>
       <c r="S30">
         <v>100</v>
       </c>
       <c r="T30">
+        <v>100</v>
+      </c>
+      <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
         <v>90.2</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>89.59999999999999</v>
       </c>
-      <c r="V30">
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5177,31 +5772,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5398,28 +5993,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>27</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>88.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="G8" s="2">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5430,21 +6025,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C9">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G9" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="H9">
+        <v>7.9</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5479,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -5513,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1AM - Estadisticos 20231.xlsx
+++ b/grupos/1AM - Estadisticos 20231.xlsx
@@ -884,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -893,10 +893,10 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE4">
         <v>5</v>
@@ -988,22 +988,22 @@
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE5">
         <v>10</v>
       </c>
       <c r="AF5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1086,25 +1086,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1190,16 +1190,16 @@
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>10</v>
       </c>
       <c r="AD7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE7">
         <v>10</v>
@@ -1288,25 +1288,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1389,25 +1389,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA9">
         <v>5</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD9">
         <v>5</v>
       </c>
       <c r="AE9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1591,25 +1591,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1692,25 +1692,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1793,19 +1793,19 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>10</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE13">
         <v>10</v>
@@ -1897,16 +1897,16 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE14">
         <v>10</v>
@@ -2096,22 +2096,22 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF16">
         <v>10</v>
@@ -2197,25 +2197,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2298,25 +2298,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC18">
         <v>10</v>
       </c>
       <c r="AD18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE18">
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2399,25 +2399,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD19">
         <v>5</v>
       </c>
       <c r="AE19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2500,25 +2500,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2601,25 +2601,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD21">
         <v>5</v>
       </c>
       <c r="AE21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2708,10 +2708,10 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>5</v>
@@ -2720,7 +2720,7 @@
         <v>5</v>
       </c>
       <c r="AF22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2913,7 +2913,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD24">
         <v>5</v>
@@ -2922,7 +2922,7 @@
         <v>5</v>
       </c>
       <c r="AF24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -3005,16 +3005,16 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD25">
         <v>5</v>
@@ -3023,7 +3023,7 @@
         <v>10</v>
       </c>
       <c r="AF25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3106,25 +3106,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD26">
         <v>5</v>
       </c>
       <c r="AE26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3207,25 +3207,25 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD27">
         <v>5</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3308,25 +3308,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3409,25 +3409,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3510,25 +3510,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA30">
         <v>5</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD30">
         <v>5</v>
       </c>
       <c r="AE30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -5822,7 +5822,7 @@
         <v>51.9</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>29.6</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5886,7 +5886,7 @@
         <v>25.9</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>22.2</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         <v>18.5</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5982,7 +5982,7 @@
         <v>14.8</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6046,7 +6046,7 @@
         <v>11.1</v>
       </c>
       <c r="H9">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="I9">
         <v>0</v>

--- a/grupos/1AM - Estadisticos 20231.xlsx
+++ b/grupos/1AM - Estadisticos 20231.xlsx
@@ -884,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -893,10 +893,10 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE4">
         <v>5</v>
@@ -988,22 +988,22 @@
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE5">
         <v>10</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1086,25 +1086,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1190,16 +1190,16 @@
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE7">
         <v>10</v>
@@ -1288,25 +1288,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1389,25 +1389,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>5</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD9">
         <v>5</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1591,25 +1591,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD11">
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1692,25 +1692,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1793,19 +1793,19 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>10</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE13">
         <v>10</v>
@@ -1897,16 +1897,16 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE14">
         <v>10</v>
@@ -2096,22 +2096,22 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16">
         <v>10</v>
@@ -2197,25 +2197,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2298,25 +2298,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>10</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE18">
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2399,25 +2399,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD19">
         <v>5</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2500,25 +2500,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB20">
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2601,25 +2601,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD21">
         <v>5</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2708,10 +2708,10 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD22">
         <v>5</v>
@@ -2720,7 +2720,7 @@
         <v>5</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2913,7 +2913,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD24">
         <v>5</v>
@@ -2922,7 +2922,7 @@
         <v>5</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -3005,16 +3005,16 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD25">
         <v>5</v>
@@ -3023,7 +3023,7 @@
         <v>10</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3106,25 +3106,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD26">
         <v>5</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3207,25 +3207,25 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD27">
         <v>5</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3308,25 +3308,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3409,25 +3409,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3510,25 +3510,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>5</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD30">
         <v>5</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -5822,7 +5822,7 @@
         <v>51.9</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>29.6</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5886,7 +5886,7 @@
         <v>25.9</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>22.2</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         <v>18.5</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5982,7 +5982,7 @@
         <v>14.8</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6046,7 +6046,7 @@
         <v>11.1</v>
       </c>
       <c r="H9">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="I9">
         <v>0</v>
